--- a/02_Azure/ログ要約資料（Azure).xlsx
+++ b/02_Azure/ログ要約資料（Azure).xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\望都\02_Azure\OpenAI\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\learning_products\02_Azure\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40FA9DAB-A881-4035-8604-568640230A39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5022ED7-74AD-4D12-BC88-65C2C6E9DC24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" firstSheet="4" activeTab="7" xr2:uid="{0A91C367-6FA2-4704-B5D5-1735E3BB6AAE}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{0A91C367-6FA2-4704-B5D5-1735E3BB6AAE}"/>
   </bookViews>
   <sheets>
     <sheet name="全体概要図" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="437" uniqueCount="346">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="437" uniqueCount="343">
   <si>
     <t>PC（揮発性）</t>
   </si>
@@ -58,9 +58,6 @@
     <t>Azure Blob Storage（input）</t>
   </si>
   <si>
-    <t xml:space="preserve"> └─ container: logs-input/raw-logs/</t>
-  </si>
-  <si>
     <t xml:space="preserve">        │ Blob Trigger</t>
   </si>
   <si>
@@ -85,9 +82,6 @@
     <t>Azure Blob Storage（output）</t>
   </si>
   <si>
-    <t xml:space="preserve"> └─ container: logs-output/summaries/</t>
-  </si>
-  <si>
     <t xml:space="preserve"> └─ 要約結果をダウンロード</t>
   </si>
   <si>
@@ -126,9 +120,6 @@
     <t>入力/出力</t>
   </si>
   <si>
-    <t>stlgsmprdjpe</t>
-  </si>
-  <si>
     <t>Blob Storage</t>
   </si>
   <si>
@@ -138,18 +129,12 @@
     <t>入力ログ</t>
   </si>
   <si>
-    <t>logs-input</t>
-  </si>
-  <si>
     <t>raw-logs/ 配下に保存</t>
   </si>
   <si>
     <t>出力要約</t>
   </si>
   <si>
-    <t>logs-output</t>
-  </si>
-  <si>
     <t>summaries/ 配下に保存</t>
   </si>
   <si>
@@ -159,9 +144,6 @@
     <t>ログ要約処理</t>
   </si>
   <si>
-    <t>func-lgsm-prd-jpe</t>
-  </si>
-  <si>
     <t>Blob Trigger</t>
   </si>
   <si>
@@ -171,9 +153,6 @@
     <t>推論</t>
   </si>
   <si>
-    <t>aoai-lgsm-prd-jpe</t>
-  </si>
-  <si>
     <t>GPT‑4o/4.1</t>
   </si>
   <si>
@@ -183,9 +162,6 @@
     <t>モデル</t>
   </si>
   <si>
-    <t>gpt-4o-logsummary</t>
-  </si>
-  <si>
     <t>GPT‑4o</t>
   </si>
   <si>
@@ -195,13 +171,7 @@
     <t>出力コンテナ</t>
   </si>
   <si>
-    <t>OUTPUT_CONTAINER=logs-output</t>
-  </si>
-  <si>
     <t>モデル名</t>
-  </si>
-  <si>
-    <t>OPENAI_DEPLOYMENT_NAME=gpt-4o-logsummary</t>
   </si>
   <si>
     <t>Azure 命名規則</t>
@@ -224,9 +194,6 @@
   </si>
   <si>
     <t xml:space="preserve">      "direction": "in",</t>
-  </si>
-  <si>
-    <t xml:space="preserve">      "path": "logs-input/raw-logs/{name}",</t>
   </si>
   <si>
     <t xml:space="preserve">    }</t>
@@ -576,56 +543,6 @@
   </si>
   <si>
     <t>⑥ 動作確認</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">1. PC → </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-        <family val="2"/>
-      </rPr>
-      <t>logs-input/raw-logs/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="游ゴシック"/>
-        <family val="2"/>
-        <charset val="128"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> に Java ビルドログをアップロード</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>2. 数秒後、</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-        <family val="2"/>
-      </rPr>
-      <t>logs-output/summaries/xxx.log.summary.txt</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="游ゴシック"/>
-        <family val="2"/>
-        <charset val="128"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> が生成</t>
-    </r>
   </si>
   <si>
     <r>
@@ -677,12 +594,6 @@
     <t xml:space="preserve"> Azure Blob Storage（Input）</t>
   </si>
   <si>
-    <t xml:space="preserve"> container: logs-input</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> prefix: raw-logs/</t>
-  </si>
-  <si>
     <t xml:space="preserve">            │ Blob Trigger</t>
   </si>
   <si>
@@ -707,12 +618,6 @@
     <t xml:space="preserve"> Azure Blob Storage（Output）</t>
   </si>
   <si>
-    <t xml:space="preserve"> container: logs-output</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> prefix: summaries/</t>
-  </si>
-  <si>
     <t>(6) PC（揮発性）</t>
   </si>
   <si>
@@ -753,12 +658,6 @@
     <t xml:space="preserve">  - Lifecycle Policy:</t>
   </si>
   <si>
-    <t xml:space="preserve">      logs-input/raw-logs/ → 1日で削除</t>
-  </si>
-  <si>
-    <t xml:space="preserve">      logs-output/summaries/ → 7日で削除</t>
-  </si>
-  <si>
     <t xml:space="preserve"> Azure Functions（func-lgsm-prd-jpe）</t>
   </si>
   <si>
@@ -861,9 +760,6 @@
     <t>logs-output を7日で削除するポリシーを設定</t>
   </si>
   <si>
-    <t>ストレージに stlgsmprdjpe を指定</t>
-  </si>
-  <si>
     <t>消費プランで作成</t>
   </si>
   <si>
@@ -873,15 +769,9 @@
     <t>アプリ設定 OPENAI_API_KEY を設定</t>
   </si>
   <si>
-    <t>アプリ設定 OPENAI_DEPLOYMENT_NAME=gpt-4o-logsummary を設定</t>
-  </si>
-  <si>
     <t>アプリ設定 MAX_LINES_PER_CHUNK=4000 を設定</t>
   </si>
   <si>
-    <t>アプリ設定 OUTPUT_CONTAINER=logs-output を設定</t>
-  </si>
-  <si>
     <t>マネージドIDを有効化</t>
   </si>
   <si>
@@ -891,9 +781,6 @@
     <t>Function App に Cognitive Services OpenAI User を付与</t>
   </si>
   <si>
-    <t>function.json のパスを logs-input/raw-logs/{name} に設定</t>
-  </si>
-  <si>
     <t>Python requirements.txt をデプロイ</t>
   </si>
   <si>
@@ -904,12 +791,6 @@
   </si>
   <si>
     <t>動作確認</t>
-  </si>
-  <si>
-    <t>logs-input/raw-logs/ に Java ビルドログをアップロード</t>
-  </si>
-  <si>
-    <t>logs-output/summaries/ に summary ファイルが生成されることを確認</t>
   </si>
   <si>
     <t>要約内容が「致命的エラー＋原因候補」になっていることを確認</t>
@@ -945,10 +826,6 @@
   </si>
   <si>
     <t>rg-lgsm-prd-jpe を作成する</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>rg-lgsm-prd-jpe</t>
     <phoneticPr fontId="3"/>
   </si>
   <si>
@@ -1124,19 +1001,11 @@
     <phoneticPr fontId="3"/>
   </si>
   <si>
-    <t>gpt-4o-logsummary</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
     <t>MAX_LINES_PER_CHUNK</t>
     <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>OUTPUT_CONTAINER</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>logs-output</t>
     <phoneticPr fontId="3"/>
   </si>
   <si>
@@ -1192,17 +1061,6 @@
     <phoneticPr fontId="3"/>
   </si>
   <si>
-    <t>Function App に Storage Blob Data Reader を付与（logs-input）</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>Function App に Storage Blob Data Contributor を付与（logs-output）</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>18,Resource Group,リソースグループ rg-lgsm-prd-jpe,18,全リソース削除後に最後に削除</t>
-  </si>
-  <si>
     <t>No</t>
   </si>
   <si>
@@ -1251,39 +1109,21 @@
     <t>Function App削除後に不要</t>
   </si>
   <si>
-    <t>OpenAI Deployment（gpt-4o-logsummary）</t>
-  </si>
-  <si>
     <t>モデルデプロイを先に削除</t>
   </si>
   <si>
-    <t>Azure OpenAI リソース（aoai-lgsm-prd-jpe）</t>
-  </si>
-  <si>
     <t>依存するデプロイ削除後に削除可能</t>
   </si>
   <si>
     <t>Storage</t>
   </si>
   <si>
-    <t>logs-output/summaries/ の中身</t>
-  </si>
-  <si>
     <t>必要ならバックアップしてから削除</t>
   </si>
   <si>
-    <t>logs-input/raw-logs/ の中身</t>
-  </si>
-  <si>
-    <t>Blob コンテナ logs-output</t>
-  </si>
-  <si>
     <t>中身削除後でないと削除不可</t>
   </si>
   <si>
-    <t>Blob コンテナ logs-input</t>
-  </si>
-  <si>
     <t>azure-webjobs-hosts コンテナ</t>
   </si>
   <si>
@@ -1327,6 +1167,186 @@
   </si>
   <si>
     <t>RBAC</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> └─ container:xxxx-xxxxxx/xxx-xxxx/</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> └─ container: xxxx-xxxxx/xxxxxxxxx/</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>xx-xxxx-xxx-xxx</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>xxxxxxxxxxxxx</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>xxxx-xxxx</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>xxxx-xxxxxx</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>xxxx-xxxx-xxx-xxx</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>xxx-xx-xxxxxxxxxx</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>OUTPUT_CONTAINER=xxxx-xxxxxxx</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>OPENAI_DEPLOYMENT_NAME=xxx-xx-xxxxxxxxxx</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>ストレージに xxxxxxxxxxxx を指定</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>アプリ設定 OPENAI_DEPLOYMENT_NAME=xxx-xx-xxxxxxxxxx を設定</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>アプリ設定 OUTPUT_CONTAINER=xxxx-xxxxxx を設定</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>Function App に Storage Blob Data Reader を付与（lxxxx-xxxxx）</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>Function App に Storage Blob Data Contributor を付与（xxxx-xxxxxxx）</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>function.json のパスを xxxx-xxxxx/xxx-xxxx/{name} に設定</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>xxxx-xxxxx/xxx-xxxx/ に Java ビルドログをアップロード</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>xxxx-xxxxxx/xxxxxxxxx/ に summary ファイルが生成されることを確認</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t xml:space="preserve">      "path": "xxxx-xxxxx/xxx-xxxx/{name}",</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">1. PC → </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>xxxx-xxxxx/xxx-xxxx/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> に Java ビルドログをアップロード</t>
+    </r>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <r>
+      <t>2. 数秒後、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>xxxx-xxxxxx/xxxxxxxxx/xxx.xxx.xxxxxxx.txt</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> が生成</t>
+    </r>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> container: xxxx-xxxxx</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> prefix: xxx-xxxx/</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> container: xxxx-xxxxxx</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> prefix: xxxxxxxxx/</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t xml:space="preserve">      xxxx-xxxxx/xxx-xxxx/ → 1日で削除</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t xml:space="preserve">      xxxx-xxxxxx/xxxxxxxxx/ → 7日で削除</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>OpenAI Deployment（xxx-xx-xxxxxxxxxx）</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>Azure OpenAI リソース（xxxx-xxxx-xxx-xxx）</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>xxxx-xxxxxx/xxxxxxxxx/ の中身</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>xxxx-xxxxx/xxx-xxxx/ の中身</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>Blob コンテナxxxx-xxxxxx</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>Blob コンテナ xxxx-xxxxx</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>18,Resource Group,リソースグループ xx-xxxx-xxx-xxx,18,全リソース削除後に最後に削除</t>
     <phoneticPr fontId="3"/>
   </si>
 </sst>
@@ -1858,12 +1878,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" s="12" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1888,12 +1908,12 @@
     </row>
     <row r="7" spans="1:1">
       <c r="A7" t="s">
-        <v>5</v>
+        <v>309</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:1">
@@ -1903,32 +1923,32 @@
     </row>
     <row r="10" spans="1:1">
       <c r="A10" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="14" spans="1:1">
       <c r="A14" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="16" spans="1:1">
@@ -1943,12 +1963,12 @@
     </row>
     <row r="18" spans="1:1">
       <c r="A18" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" t="s">
-        <v>14</v>
+        <v>310</v>
       </c>
     </row>
     <row r="20" spans="1:1">
@@ -1968,7 +1988,7 @@
     </row>
     <row r="23" spans="1:1">
       <c r="A23" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>
@@ -1990,142 +2010,142 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="D2" s="4" t="s">
         <v>19</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>311</v>
+      </c>
+      <c r="D3" s="2" t="s">
         <v>22</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>256</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>312</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>25</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="2" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>31</v>
+        <v>313</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="B6" s="2" t="s">
-        <v>33</v>
-      </c>
       <c r="C6" s="3" t="s">
-        <v>34</v>
+        <v>314</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="2" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>38</v>
+        <v>315</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="2" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>42</v>
+        <v>315</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="2" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>46</v>
+        <v>316</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="2" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>50</v>
+        <v>317</v>
       </c>
       <c r="D10" s="2"/>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="2" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>52</v>
+        <v>318</v>
       </c>
       <c r="D11" s="2"/>
     </row>
@@ -2147,350 +2167,350 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" t="s">
-        <v>254</v>
+        <v>229</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="15" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B2" s="15" t="s">
-        <v>219</v>
+        <v>200</v>
       </c>
       <c r="C2" s="15" t="s">
-        <v>220</v>
+        <v>201</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="13" t="s">
-        <v>221</v>
+        <v>202</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>255</v>
+        <v>230</v>
       </c>
       <c r="C3" s="13"/>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="13" t="s">
-        <v>222</v>
+        <v>203</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>257</v>
+        <v>231</v>
       </c>
       <c r="C4" s="13"/>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="13" t="s">
-        <v>222</v>
+        <v>203</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>223</v>
+        <v>204</v>
       </c>
       <c r="C5" s="13"/>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="13" t="s">
-        <v>224</v>
+        <v>205</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>258</v>
+        <v>232</v>
       </c>
       <c r="C6" s="13"/>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="13" t="s">
-        <v>224</v>
+        <v>205</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>225</v>
+        <v>206</v>
       </c>
       <c r="C7" s="13"/>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="13" t="s">
-        <v>224</v>
+        <v>205</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>259</v>
+        <v>233</v>
       </c>
       <c r="C8" s="13"/>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" s="13" t="s">
-        <v>224</v>
+        <v>205</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>260</v>
+        <v>234</v>
       </c>
       <c r="C9" s="13"/>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" s="13" t="s">
-        <v>226</v>
+        <v>207</v>
       </c>
       <c r="B10" s="13" t="s">
-        <v>227</v>
+        <v>208</v>
       </c>
       <c r="C10" s="13"/>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="13" t="s">
-        <v>226</v>
+        <v>207</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>228</v>
+        <v>209</v>
       </c>
       <c r="C11" s="13"/>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="13" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="B12" s="13" t="s">
-        <v>261</v>
+        <v>235</v>
       </c>
       <c r="C12" s="13"/>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="13" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="B13" s="13" t="s">
-        <v>262</v>
+        <v>236</v>
       </c>
       <c r="C13" s="13"/>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="13" t="s">
-        <v>264</v>
+        <v>238</v>
       </c>
       <c r="B14" s="13" t="s">
-        <v>263</v>
+        <v>237</v>
       </c>
       <c r="C14" s="13"/>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="13" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="B15" s="13" t="s">
-        <v>265</v>
+        <v>239</v>
       </c>
       <c r="C15" s="13"/>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="13" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="B16" s="13" t="s">
-        <v>229</v>
+        <v>319</v>
       </c>
       <c r="C16" s="13"/>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="13" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>230</v>
+        <v>210</v>
       </c>
       <c r="C17" s="13"/>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="13" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>231</v>
+        <v>211</v>
       </c>
       <c r="C18" s="13"/>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="13" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="B19" s="13" t="s">
-        <v>232</v>
+        <v>212</v>
       </c>
       <c r="C19" s="13"/>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="13" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="B20" s="13" t="s">
-        <v>233</v>
+        <v>320</v>
       </c>
       <c r="C20" s="13"/>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" s="13" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="B21" s="13" t="s">
-        <v>234</v>
+        <v>213</v>
       </c>
       <c r="C21" s="13"/>
     </row>
     <row r="22" spans="1:3">
       <c r="A22" s="13" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="B22" s="13" t="s">
-        <v>235</v>
+        <v>321</v>
       </c>
       <c r="C22" s="13"/>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="13" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="B23" s="13" t="s">
-        <v>236</v>
+        <v>214</v>
       </c>
       <c r="C23" s="13"/>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="13" t="s">
-        <v>237</v>
+        <v>215</v>
       </c>
       <c r="B24" s="13" t="s">
-        <v>301</v>
+        <v>322</v>
       </c>
       <c r="C24" s="13"/>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="13" t="s">
-        <v>237</v>
+        <v>215</v>
       </c>
       <c r="B25" s="13" t="s">
-        <v>302</v>
+        <v>323</v>
       </c>
       <c r="C25" s="13"/>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="13" t="s">
-        <v>237</v>
+        <v>215</v>
       </c>
       <c r="B26" s="13" t="s">
-        <v>238</v>
+        <v>216</v>
       </c>
       <c r="C26" s="13"/>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="13" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="B27" s="13" t="s">
-        <v>154</v>
+        <v>143</v>
       </c>
       <c r="C27" s="13"/>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="13" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="B28" s="13" t="s">
-        <v>239</v>
+        <v>324</v>
       </c>
       <c r="C28" s="13"/>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="13" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="B29" s="13" t="s">
-        <v>240</v>
+        <v>217</v>
       </c>
       <c r="C29" s="13"/>
     </row>
     <row r="30" spans="1:3">
       <c r="A30" s="13" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="B30" s="13" t="s">
-        <v>241</v>
+        <v>218</v>
       </c>
       <c r="C30" s="13"/>
     </row>
     <row r="31" spans="1:3">
       <c r="A31" s="13" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="B31" s="13" t="s">
-        <v>242</v>
+        <v>219</v>
       </c>
       <c r="C31" s="13"/>
     </row>
     <row r="32" spans="1:3">
       <c r="A32" s="13" t="s">
-        <v>243</v>
+        <v>220</v>
       </c>
       <c r="B32" s="13" t="s">
-        <v>244</v>
+        <v>325</v>
       </c>
       <c r="C32" s="13"/>
     </row>
     <row r="33" spans="1:3">
       <c r="A33" s="13" t="s">
-        <v>243</v>
+        <v>220</v>
       </c>
       <c r="B33" s="13" t="s">
-        <v>245</v>
+        <v>326</v>
       </c>
       <c r="C33" s="13"/>
     </row>
     <row r="34" spans="1:3">
       <c r="A34" s="13" t="s">
-        <v>243</v>
+        <v>220</v>
       </c>
       <c r="B34" s="13" t="s">
-        <v>246</v>
+        <v>221</v>
       </c>
       <c r="C34" s="13"/>
     </row>
     <row r="35" spans="1:3">
       <c r="A35" s="13" t="s">
-        <v>247</v>
+        <v>222</v>
       </c>
       <c r="B35" s="13" t="s">
-        <v>248</v>
+        <v>223</v>
       </c>
       <c r="C35" s="13"/>
     </row>
     <row r="36" spans="1:3">
       <c r="A36" s="13" t="s">
-        <v>247</v>
+        <v>222</v>
       </c>
       <c r="B36" s="13" t="s">
-        <v>249</v>
+        <v>224</v>
       </c>
       <c r="C36" s="13"/>
     </row>
     <row r="37" spans="1:3">
       <c r="A37" s="13" t="s">
-        <v>247</v>
+        <v>222</v>
       </c>
       <c r="B37" s="13" t="s">
-        <v>250</v>
+        <v>225</v>
       </c>
       <c r="C37" s="13"/>
     </row>
     <row r="38" spans="1:3">
       <c r="A38" s="14" t="s">
-        <v>251</v>
+        <v>226</v>
       </c>
       <c r="B38" s="13" t="s">
-        <v>252</v>
+        <v>227</v>
       </c>
       <c r="C38" s="13"/>
     </row>
     <row r="39" spans="1:3">
       <c r="A39" s="14" t="s">
-        <v>251</v>
+        <v>226</v>
       </c>
       <c r="B39" s="13" t="s">
-        <v>253</v>
+        <v>228</v>
       </c>
       <c r="C39" s="13"/>
     </row>
@@ -2510,42 +2530,42 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="5" t="s">
-        <v>269</v>
+        <v>243</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" s="6" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" s="6" t="s">
-        <v>270</v>
+        <v>244</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" s="6" t="s">
-        <v>271</v>
+        <v>245</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" s="6" t="s">
-        <v>272</v>
+        <v>246</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" s="6" t="s">
-        <v>273</v>
+        <v>247</v>
       </c>
     </row>
     <row r="10" spans="1:1">
@@ -2553,142 +2573,142 @@
     </row>
     <row r="12" spans="1:1">
       <c r="A12" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" s="5" t="s">
-        <v>274</v>
+        <v>248</v>
       </c>
     </row>
     <row r="14" spans="1:1">
       <c r="A14" s="6" t="s">
-        <v>275</v>
+        <v>249</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" s="6" t="s">
-        <v>276</v>
+        <v>250</v>
       </c>
     </row>
     <row r="16" spans="1:1">
       <c r="A16" s="6" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" s="6" t="s">
-        <v>277</v>
+        <v>251</v>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18" s="6" t="s">
-        <v>278</v>
+        <v>252</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" s="6" t="s">
-        <v>58</v>
+        <v>48</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" s="6" t="s">
-        <v>59</v>
+        <v>327</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" s="6" t="s">
-        <v>279</v>
+        <v>253</v>
       </c>
     </row>
     <row r="22" spans="1:1">
       <c r="A22" s="6" t="s">
-        <v>60</v>
+        <v>49</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" s="6" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
     </row>
     <row r="24" spans="1:1">
       <c r="A24" s="7" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
     </row>
     <row r="26" spans="1:1">
       <c r="A26" t="s">
-        <v>280</v>
+        <v>254</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" s="5" t="s">
-        <v>281</v>
+        <v>255</v>
       </c>
     </row>
     <row r="28" spans="1:1">
       <c r="A28" s="6" t="s">
-        <v>282</v>
+        <v>256</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" s="7" t="s">
-        <v>283</v>
+        <v>257</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" t="s">
-        <v>64</v>
+        <v>53</v>
       </c>
     </row>
     <row r="32" spans="1:1">
       <c r="A32" s="5" t="s">
-        <v>274</v>
+        <v>248</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" s="6" t="s">
-        <v>284</v>
+        <v>258</v>
       </c>
     </row>
     <row r="34" spans="1:1">
       <c r="A34" s="7" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
     </row>
     <row r="36" spans="1:1">
       <c r="A36" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" s="5" t="s">
-        <v>285</v>
+        <v>259</v>
       </c>
     </row>
     <row r="38" spans="1:1">
       <c r="A38" s="6" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" s="6" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
     </row>
     <row r="40" spans="1:1">
       <c r="A40" s="6" t="s">
-        <v>67</v>
+        <v>56</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" s="6" t="s">
-        <v>68</v>
+        <v>57</v>
       </c>
     </row>
     <row r="42" spans="1:1">
       <c r="A42" s="6" t="s">
-        <v>69</v>
+        <v>58</v>
       </c>
     </row>
     <row r="43" spans="1:1">
@@ -2696,32 +2716,32 @@
     </row>
     <row r="44" spans="1:1">
       <c r="A44" s="6" t="s">
-        <v>70</v>
+        <v>59</v>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45" s="6" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" s="6" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
     </row>
     <row r="47" spans="1:1">
       <c r="A47" s="6" t="s">
-        <v>73</v>
+        <v>62</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" s="6" t="s">
-        <v>74</v>
+        <v>63</v>
       </c>
     </row>
     <row r="49" spans="1:1">
       <c r="A49" s="6" t="s">
-        <v>75</v>
+        <v>64</v>
       </c>
     </row>
     <row r="50" spans="1:1">
@@ -2729,7 +2749,7 @@
     </row>
     <row r="51" spans="1:1">
       <c r="A51" s="6" t="s">
-        <v>76</v>
+        <v>65</v>
       </c>
     </row>
     <row r="52" spans="1:1">
@@ -2740,17 +2760,17 @@
     </row>
     <row r="54" spans="1:1">
       <c r="A54" s="6" t="s">
-        <v>77</v>
+        <v>66</v>
       </c>
     </row>
     <row r="55" spans="1:1">
       <c r="A55" s="6" t="s">
-        <v>78</v>
+        <v>67</v>
       </c>
     </row>
     <row r="56" spans="1:1">
       <c r="A56" s="6" t="s">
-        <v>79</v>
+        <v>68</v>
       </c>
     </row>
     <row r="57" spans="1:1">
@@ -2758,7 +2778,7 @@
     </row>
     <row r="58" spans="1:1">
       <c r="A58" s="6" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
     </row>
     <row r="59" spans="1:1">
@@ -2766,12 +2786,12 @@
     </row>
     <row r="60" spans="1:1">
       <c r="A60" s="6" t="s">
-        <v>81</v>
+        <v>70</v>
       </c>
     </row>
     <row r="61" spans="1:1">
       <c r="A61" s="6" t="s">
-        <v>82</v>
+        <v>71</v>
       </c>
     </row>
     <row r="62" spans="1:1">
@@ -2779,17 +2799,17 @@
     </row>
     <row r="63" spans="1:1">
       <c r="A63" s="6" t="s">
-        <v>83</v>
+        <v>72</v>
       </c>
     </row>
     <row r="64" spans="1:1">
       <c r="A64" s="6" t="s">
-        <v>84</v>
+        <v>73</v>
       </c>
     </row>
     <row r="65" spans="1:1">
       <c r="A65" s="6" t="s">
-        <v>85</v>
+        <v>74</v>
       </c>
     </row>
     <row r="66" spans="1:1">
@@ -2797,32 +2817,32 @@
     </row>
     <row r="67" spans="1:1">
       <c r="A67" s="6" t="s">
-        <v>86</v>
+        <v>75</v>
       </c>
     </row>
     <row r="68" spans="1:1">
       <c r="A68" s="6" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
     </row>
     <row r="69" spans="1:1">
       <c r="A69" s="6" t="s">
-        <v>88</v>
+        <v>77</v>
       </c>
     </row>
     <row r="70" spans="1:1">
       <c r="A70" s="6" t="s">
-        <v>89</v>
+        <v>78</v>
       </c>
     </row>
     <row r="71" spans="1:1">
       <c r="A71" s="6" t="s">
-        <v>90</v>
+        <v>79</v>
       </c>
     </row>
     <row r="72" spans="1:1">
       <c r="A72" s="6" t="s">
-        <v>91</v>
+        <v>80</v>
       </c>
     </row>
     <row r="73" spans="1:1">
@@ -2830,12 +2850,12 @@
     </row>
     <row r="74" spans="1:1">
       <c r="A74" s="6" t="s">
-        <v>92</v>
+        <v>81</v>
       </c>
     </row>
     <row r="75" spans="1:1">
       <c r="A75" s="6" t="s">
-        <v>93</v>
+        <v>82</v>
       </c>
     </row>
     <row r="76" spans="1:1">
@@ -2843,17 +2863,17 @@
     </row>
     <row r="77" spans="1:1">
       <c r="A77" s="6" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
     </row>
     <row r="78" spans="1:1">
       <c r="A78" s="6" t="s">
-        <v>95</v>
+        <v>84</v>
       </c>
     </row>
     <row r="79" spans="1:1">
       <c r="A79" s="6" t="s">
-        <v>96</v>
+        <v>85</v>
       </c>
     </row>
     <row r="80" spans="1:1">
@@ -2861,7 +2881,7 @@
     </row>
     <row r="81" spans="1:1">
       <c r="A81" s="6" t="s">
-        <v>97</v>
+        <v>86</v>
       </c>
     </row>
     <row r="82" spans="1:1">
@@ -2872,32 +2892,32 @@
     </row>
     <row r="84" spans="1:1">
       <c r="A84" s="6" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
     </row>
     <row r="85" spans="1:1">
       <c r="A85" s="6" t="s">
-        <v>99</v>
+        <v>88</v>
       </c>
     </row>
     <row r="86" spans="1:1">
       <c r="A86" s="6" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
     </row>
     <row r="87" spans="1:1">
       <c r="A87" s="6" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
     </row>
     <row r="88" spans="1:1">
       <c r="A88" s="6" t="s">
-        <v>101</v>
+        <v>90</v>
       </c>
     </row>
     <row r="89" spans="1:1">
       <c r="A89" s="6" t="s">
-        <v>102</v>
+        <v>91</v>
       </c>
     </row>
     <row r="90" spans="1:1">
@@ -2908,37 +2928,37 @@
     </row>
     <row r="92" spans="1:1">
       <c r="A92" s="6" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
     </row>
     <row r="93" spans="1:1">
       <c r="A93" s="6" t="s">
-        <v>103</v>
+        <v>92</v>
       </c>
     </row>
     <row r="94" spans="1:1">
       <c r="A94" s="6" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
     </row>
     <row r="95" spans="1:1">
       <c r="A95" s="6" t="s">
-        <v>104</v>
+        <v>93</v>
       </c>
     </row>
     <row r="96" spans="1:1">
       <c r="A96" s="6" t="s">
-        <v>105</v>
+        <v>94</v>
       </c>
     </row>
     <row r="97" spans="1:1">
       <c r="A97" s="6" t="s">
-        <v>106</v>
+        <v>95</v>
       </c>
     </row>
     <row r="98" spans="1:1">
       <c r="A98" s="6" t="s">
-        <v>107</v>
+        <v>96</v>
       </c>
     </row>
     <row r="99" spans="1:1">
@@ -2946,27 +2966,27 @@
     </row>
     <row r="100" spans="1:1">
       <c r="A100" s="6" t="s">
-        <v>108</v>
+        <v>97</v>
       </c>
     </row>
     <row r="101" spans="1:1">
       <c r="A101" s="6" t="s">
-        <v>109</v>
+        <v>98</v>
       </c>
     </row>
     <row r="102" spans="1:1">
       <c r="A102" s="6" t="s">
-        <v>110</v>
+        <v>99</v>
       </c>
     </row>
     <row r="103" spans="1:1">
       <c r="A103" s="6" t="s">
-        <v>111</v>
+        <v>100</v>
       </c>
     </row>
     <row r="104" spans="1:1">
       <c r="A104" s="6" t="s">
-        <v>112</v>
+        <v>101</v>
       </c>
     </row>
     <row r="105" spans="1:1">
@@ -2974,7 +2994,7 @@
     </row>
     <row r="106" spans="1:1">
       <c r="A106" s="6" t="s">
-        <v>113</v>
+        <v>102</v>
       </c>
     </row>
     <row r="107" spans="1:1">
@@ -2982,22 +3002,22 @@
     </row>
     <row r="108" spans="1:1">
       <c r="A108" s="6" t="s">
-        <v>114</v>
+        <v>103</v>
       </c>
     </row>
     <row r="109" spans="1:1">
       <c r="A109" s="6" t="s">
-        <v>115</v>
+        <v>104</v>
       </c>
     </row>
     <row r="110" spans="1:1">
       <c r="A110" s="6" t="s">
-        <v>116</v>
+        <v>105</v>
       </c>
     </row>
     <row r="111" spans="1:1" ht="180">
       <c r="A111" s="8" t="s">
-        <v>117</v>
+        <v>106</v>
       </c>
     </row>
     <row r="112" spans="1:1">
@@ -3005,22 +3025,22 @@
     </row>
     <row r="113" spans="1:1">
       <c r="A113" s="6" t="s">
-        <v>118</v>
+        <v>107</v>
       </c>
     </row>
     <row r="114" spans="1:1">
       <c r="A114" s="6" t="s">
-        <v>119</v>
+        <v>108</v>
       </c>
     </row>
     <row r="115" spans="1:1">
       <c r="A115" s="6" t="s">
-        <v>120</v>
+        <v>109</v>
       </c>
     </row>
     <row r="116" spans="1:1">
       <c r="A116" s="6" t="s">
-        <v>60</v>
+        <v>49</v>
       </c>
     </row>
     <row r="117" spans="1:1">
@@ -3028,42 +3048,42 @@
     </row>
     <row r="118" spans="1:1">
       <c r="A118" s="6" t="s">
-        <v>121</v>
+        <v>110</v>
       </c>
     </row>
     <row r="119" spans="1:1">
       <c r="A119" s="6" t="s">
-        <v>122</v>
+        <v>111</v>
       </c>
     </row>
     <row r="120" spans="1:1">
       <c r="A120" s="6" t="s">
-        <v>123</v>
+        <v>112</v>
       </c>
     </row>
     <row r="121" spans="1:1">
       <c r="A121" s="6" t="s">
-        <v>124</v>
+        <v>113</v>
       </c>
     </row>
     <row r="122" spans="1:1">
       <c r="A122" s="6" t="s">
-        <v>125</v>
+        <v>114</v>
       </c>
     </row>
     <row r="123" spans="1:1">
       <c r="A123" s="6" t="s">
-        <v>126</v>
+        <v>115</v>
       </c>
     </row>
     <row r="124" spans="1:1">
       <c r="A124" s="6" t="s">
-        <v>127</v>
+        <v>116</v>
       </c>
     </row>
     <row r="125" spans="1:1">
       <c r="A125" s="6" t="s">
-        <v>60</v>
+        <v>49</v>
       </c>
     </row>
     <row r="126" spans="1:1">
@@ -3071,12 +3091,12 @@
     </row>
     <row r="127" spans="1:1">
       <c r="A127" s="6" t="s">
-        <v>128</v>
+        <v>117</v>
       </c>
     </row>
     <row r="128" spans="1:1">
       <c r="A128" s="6" t="s">
-        <v>129</v>
+        <v>118</v>
       </c>
     </row>
     <row r="129" spans="1:1">
@@ -3084,12 +3104,12 @@
     </row>
     <row r="130" spans="1:1">
       <c r="A130" s="6" t="s">
-        <v>130</v>
+        <v>119</v>
       </c>
     </row>
     <row r="131" spans="1:1">
       <c r="A131" s="6" t="s">
-        <v>131</v>
+        <v>120</v>
       </c>
     </row>
     <row r="132" spans="1:1">
@@ -3100,27 +3120,27 @@
     </row>
     <row r="134" spans="1:1">
       <c r="A134" s="6" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
     </row>
     <row r="135" spans="1:1">
       <c r="A135" s="6" t="s">
-        <v>132</v>
+        <v>121</v>
       </c>
     </row>
     <row r="136" spans="1:1">
       <c r="A136" s="6" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
     </row>
     <row r="137" spans="1:1">
       <c r="A137" s="6" t="s">
-        <v>133</v>
+        <v>122</v>
       </c>
     </row>
     <row r="138" spans="1:1">
       <c r="A138" s="6" t="s">
-        <v>134</v>
+        <v>123</v>
       </c>
     </row>
     <row r="139" spans="1:1">
@@ -3128,17 +3148,17 @@
     </row>
     <row r="140" spans="1:1">
       <c r="A140" s="6" t="s">
-        <v>135</v>
+        <v>124</v>
       </c>
     </row>
     <row r="141" spans="1:1">
       <c r="A141" s="6" t="s">
-        <v>136</v>
+        <v>125</v>
       </c>
     </row>
     <row r="142" spans="1:1">
       <c r="A142" s="6" t="s">
-        <v>137</v>
+        <v>126</v>
       </c>
     </row>
     <row r="143" spans="1:1">
@@ -3146,22 +3166,22 @@
     </row>
     <row r="144" spans="1:1">
       <c r="A144" s="6" t="s">
-        <v>138</v>
+        <v>127</v>
       </c>
     </row>
     <row r="145" spans="1:1">
       <c r="A145" s="6" t="s">
-        <v>139</v>
+        <v>128</v>
       </c>
     </row>
     <row r="146" spans="1:1">
       <c r="A146" s="6" t="s">
-        <v>116</v>
+        <v>105</v>
       </c>
     </row>
     <row r="147" spans="1:1" ht="360">
       <c r="A147" s="9" t="s">
-        <v>286</v>
+        <v>260</v>
       </c>
     </row>
   </sheetData>
@@ -3182,92 +3202,92 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
-        <v>141</v>
+        <v>130</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="17" t="s">
-        <v>298</v>
+        <v>270</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" t="s">
-        <v>299</v>
+        <v>271</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>300</v>
+        <v>272</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" s="1" t="s">
-        <v>142</v>
+        <v>131</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" s="10" t="s">
-        <v>143</v>
+        <v>132</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" s="10" t="s">
-        <v>144</v>
+        <v>133</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" s="11" t="s">
-        <v>145</v>
+        <v>134</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" s="11" t="s">
-        <v>295</v>
+        <v>267</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" s="1" t="s">
-        <v>146</v>
+        <v>135</v>
       </c>
     </row>
     <row r="14" spans="1:1">
       <c r="A14" s="10" t="s">
-        <v>147</v>
+        <v>136</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" s="10" t="s">
-        <v>148</v>
+        <v>137</v>
       </c>
     </row>
     <row r="16" spans="1:1">
       <c r="A16" s="10" t="s">
-        <v>149</v>
+        <v>138</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>266</v>
+        <v>240</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="12" t="s">
-        <v>268</v>
+        <v>242</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="10" t="s">
-        <v>267</v>
+        <v>241</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="10" t="s">
-        <v>150</v>
+        <v>139</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="10" t="s">
-        <v>287</v>
+        <v>261</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -3275,44 +3295,44 @@
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="1" t="s">
-        <v>151</v>
+        <v>140</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="4" t="s">
-        <v>152</v>
+        <v>141</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>153</v>
+        <v>142</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="2" t="s">
-        <v>288</v>
+        <v>262</v>
       </c>
       <c r="B27" s="16" t="s">
-        <v>297</v>
+        <v>269</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="2" t="s">
-        <v>289</v>
+        <v>263</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>296</v>
+        <v>268</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="2" t="s">
-        <v>290</v>
+        <v>264</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>291</v>
+        <v>316</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="2" t="s">
-        <v>292</v>
+        <v>265</v>
       </c>
       <c r="B30" s="2">
         <v>4000</v>
@@ -3320,40 +3340,40 @@
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="2" t="s">
-        <v>293</v>
+        <v>266</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>294</v>
+        <v>314</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" s="1" t="s">
-        <v>155</v>
+        <v>144</v>
       </c>
     </row>
     <row r="34" spans="1:1">
       <c r="A34" t="s">
-        <v>156</v>
+        <v>145</v>
       </c>
     </row>
     <row r="36" spans="1:1">
       <c r="A36" s="1" t="s">
-        <v>157</v>
+        <v>146</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" s="10" t="s">
-        <v>158</v>
+        <v>328</v>
       </c>
     </row>
     <row r="38" spans="1:1">
       <c r="A38" s="10" t="s">
-        <v>159</v>
+        <v>329</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" s="10" t="s">
-        <v>160</v>
+        <v>147</v>
       </c>
     </row>
   </sheetData>
@@ -3372,162 +3392,162 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
-        <v>182</v>
+        <v>165</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" s="5" t="s">
-        <v>161</v>
+        <v>148</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="6" t="s">
-        <v>162</v>
+        <v>149</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="6" t="s">
-        <v>163</v>
+        <v>150</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" s="6" t="s">
-        <v>164</v>
+        <v>151</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" s="6" t="s">
-        <v>165</v>
+        <v>152</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" s="6" t="s">
-        <v>166</v>
+        <v>153</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" s="6" t="s">
-        <v>167</v>
+        <v>154</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" s="6" t="s">
-        <v>168</v>
+        <v>330</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" s="6" t="s">
-        <v>169</v>
+        <v>331</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" s="6" t="s">
-        <v>166</v>
+        <v>153</v>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12" s="6" t="s">
-        <v>170</v>
+        <v>155</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" s="6" t="s">
-        <v>165</v>
+        <v>152</v>
       </c>
     </row>
     <row r="14" spans="1:1">
       <c r="A14" s="6" t="s">
-        <v>166</v>
+        <v>153</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" s="6" t="s">
-        <v>171</v>
+        <v>156</v>
       </c>
     </row>
     <row r="16" spans="1:1">
       <c r="A16" s="6" t="s">
-        <v>172</v>
+        <v>157</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" s="6" t="s">
-        <v>173</v>
+        <v>158</v>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18" s="6" t="s">
-        <v>174</v>
+        <v>159</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" s="6" t="s">
-        <v>175</v>
+        <v>160</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" s="6" t="s">
-        <v>176</v>
+        <v>161</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" s="6" t="s">
-        <v>166</v>
+        <v>153</v>
       </c>
     </row>
     <row r="22" spans="1:1">
       <c r="A22" s="6" t="s">
-        <v>164</v>
+        <v>151</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" s="6" t="s">
-        <v>165</v>
+        <v>152</v>
       </c>
     </row>
     <row r="24" spans="1:1">
       <c r="A24" s="6" t="s">
-        <v>166</v>
+        <v>153</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" s="6" t="s">
-        <v>177</v>
+        <v>162</v>
       </c>
     </row>
     <row r="26" spans="1:1">
       <c r="A26" s="6" t="s">
-        <v>178</v>
+        <v>332</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" s="6" t="s">
-        <v>179</v>
+        <v>333</v>
       </c>
     </row>
     <row r="28" spans="1:1">
       <c r="A28" s="6" t="s">
-        <v>166</v>
+        <v>153</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" s="6" t="s">
-        <v>164</v>
+        <v>151</v>
       </c>
     </row>
     <row r="30" spans="1:1">
       <c r="A30" s="6" t="s">
-        <v>165</v>
+        <v>152</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" s="6" t="s">
-        <v>180</v>
+        <v>163</v>
       </c>
     </row>
     <row r="32" spans="1:1">
       <c r="A32" s="7" t="s">
-        <v>181</v>
+        <v>164</v>
       </c>
     </row>
   </sheetData>
@@ -3546,37 +3566,37 @@
   <sheetData>
     <row r="2" spans="1:1">
       <c r="A2" s="5" t="s">
-        <v>166</v>
+        <v>153</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="6" t="s">
-        <v>183</v>
+        <v>166</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="6" t="s">
-        <v>166</v>
+        <v>153</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" s="6" t="s">
-        <v>184</v>
+        <v>167</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" s="6" t="s">
-        <v>185</v>
+        <v>168</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" s="6" t="s">
-        <v>186</v>
+        <v>169</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" s="6" t="s">
-        <v>166</v>
+        <v>153</v>
       </c>
     </row>
     <row r="9" spans="1:1">
@@ -3587,57 +3607,57 @@
     </row>
     <row r="11" spans="1:1">
       <c r="A11" s="6" t="s">
-        <v>166</v>
+        <v>153</v>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12" s="6" t="s">
-        <v>187</v>
+        <v>170</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" s="6" t="s">
-        <v>166</v>
+        <v>153</v>
       </c>
     </row>
     <row r="14" spans="1:1">
       <c r="A14" s="6" t="s">
-        <v>188</v>
+        <v>171</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" s="6" t="s">
-        <v>189</v>
+        <v>172</v>
       </c>
     </row>
     <row r="16" spans="1:1">
       <c r="A16" s="6" t="s">
-        <v>190</v>
+        <v>173</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" s="6" t="s">
-        <v>191</v>
+        <v>174</v>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18" s="6" t="s">
-        <v>192</v>
+        <v>175</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" s="6" t="s">
-        <v>193</v>
+        <v>334</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" s="6" t="s">
-        <v>194</v>
+        <v>335</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" s="6" t="s">
-        <v>166</v>
+        <v>153</v>
       </c>
     </row>
     <row r="22" spans="1:1">
@@ -3648,72 +3668,72 @@
     </row>
     <row r="24" spans="1:1">
       <c r="A24" s="6" t="s">
-        <v>166</v>
+        <v>153</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" s="6" t="s">
-        <v>195</v>
+        <v>176</v>
       </c>
     </row>
     <row r="26" spans="1:1">
       <c r="A26" s="6" t="s">
-        <v>166</v>
+        <v>153</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" s="6" t="s">
-        <v>196</v>
+        <v>177</v>
       </c>
     </row>
     <row r="28" spans="1:1">
       <c r="A28" s="6" t="s">
-        <v>197</v>
+        <v>178</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" s="6" t="s">
-        <v>198</v>
+        <v>179</v>
       </c>
     </row>
     <row r="30" spans="1:1">
       <c r="A30" s="6" t="s">
-        <v>199</v>
+        <v>180</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" s="6" t="s">
-        <v>200</v>
+        <v>181</v>
       </c>
     </row>
     <row r="32" spans="1:1">
       <c r="A32" s="6" t="s">
-        <v>201</v>
+        <v>182</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" s="6" t="s">
-        <v>202</v>
+        <v>183</v>
       </c>
     </row>
     <row r="34" spans="1:1">
       <c r="A34" s="6" t="s">
-        <v>203</v>
+        <v>184</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" s="6" t="s">
-        <v>204</v>
+        <v>185</v>
       </c>
     </row>
     <row r="36" spans="1:1">
       <c r="A36" s="6" t="s">
-        <v>205</v>
+        <v>186</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" s="6" t="s">
-        <v>166</v>
+        <v>153</v>
       </c>
     </row>
     <row r="38" spans="1:1">
@@ -3724,47 +3744,47 @@
     </row>
     <row r="40" spans="1:1">
       <c r="A40" s="6" t="s">
-        <v>166</v>
+        <v>153</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" s="6" t="s">
-        <v>206</v>
+        <v>187</v>
       </c>
     </row>
     <row r="42" spans="1:1">
       <c r="A42" s="6" t="s">
-        <v>166</v>
+        <v>153</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" s="6" t="s">
-        <v>207</v>
+        <v>188</v>
       </c>
     </row>
     <row r="44" spans="1:1">
       <c r="A44" s="6" t="s">
-        <v>208</v>
+        <v>189</v>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45" s="6" t="s">
-        <v>209</v>
+        <v>190</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" s="6" t="s">
-        <v>210</v>
+        <v>191</v>
       </c>
     </row>
     <row r="47" spans="1:1">
       <c r="A47" s="6" t="s">
-        <v>211</v>
+        <v>192</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" s="6" t="s">
-        <v>166</v>
+        <v>153</v>
       </c>
     </row>
     <row r="49" spans="1:1">
@@ -3775,32 +3795,32 @@
     </row>
     <row r="51" spans="1:1">
       <c r="A51" s="6" t="s">
-        <v>166</v>
+        <v>153</v>
       </c>
     </row>
     <row r="52" spans="1:1">
       <c r="A52" s="6" t="s">
-        <v>212</v>
+        <v>193</v>
       </c>
     </row>
     <row r="53" spans="1:1">
       <c r="A53" s="6" t="s">
-        <v>166</v>
+        <v>153</v>
       </c>
     </row>
     <row r="54" spans="1:1">
       <c r="A54" s="6" t="s">
-        <v>213</v>
+        <v>194</v>
       </c>
     </row>
     <row r="55" spans="1:1">
       <c r="A55" s="6" t="s">
-        <v>214</v>
+        <v>195</v>
       </c>
     </row>
     <row r="56" spans="1:1">
       <c r="A56" s="6" t="s">
-        <v>166</v>
+        <v>153</v>
       </c>
     </row>
     <row r="57" spans="1:1">
@@ -3811,37 +3831,37 @@
     </row>
     <row r="59" spans="1:1">
       <c r="A59" s="6" t="s">
-        <v>166</v>
+        <v>153</v>
       </c>
     </row>
     <row r="60" spans="1:1">
       <c r="A60" s="6" t="s">
-        <v>215</v>
+        <v>196</v>
       </c>
     </row>
     <row r="61" spans="1:1">
       <c r="A61" s="6" t="s">
-        <v>166</v>
+        <v>153</v>
       </c>
     </row>
     <row r="62" spans="1:1">
       <c r="A62" s="6" t="s">
-        <v>216</v>
+        <v>197</v>
       </c>
     </row>
     <row r="63" spans="1:1">
       <c r="A63" s="6" t="s">
-        <v>217</v>
+        <v>198</v>
       </c>
     </row>
     <row r="64" spans="1:1">
       <c r="A64" s="6" t="s">
-        <v>218</v>
+        <v>199</v>
       </c>
     </row>
     <row r="65" spans="1:1">
       <c r="A65" s="7" t="s">
-        <v>166</v>
+        <v>153</v>
       </c>
     </row>
   </sheetData>
@@ -3862,19 +3882,19 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="15" t="s">
-        <v>304</v>
+        <v>273</v>
       </c>
       <c r="B1" s="15" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C1" s="15" t="s">
-        <v>305</v>
+        <v>274</v>
       </c>
       <c r="D1" s="15" t="s">
-        <v>306</v>
+        <v>275</v>
       </c>
       <c r="E1" s="15" t="s">
-        <v>307</v>
+        <v>276</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -3882,16 +3902,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="13" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="C2" s="13" t="s">
-        <v>308</v>
+        <v>277</v>
       </c>
       <c r="D2" s="13">
         <v>1</v>
       </c>
       <c r="E2" s="13" t="s">
-        <v>309</v>
+        <v>278</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -3899,16 +3919,16 @@
         <v>2</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="C3" s="13" t="s">
-        <v>310</v>
+        <v>279</v>
       </c>
       <c r="D3" s="13">
         <v>2</v>
       </c>
       <c r="E3" s="13" t="s">
-        <v>311</v>
+        <v>280</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -3916,16 +3936,16 @@
         <v>3</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>312</v>
+        <v>281</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>313</v>
+        <v>282</v>
       </c>
       <c r="D4" s="13">
         <v>3</v>
       </c>
       <c r="E4" s="13" t="s">
-        <v>314</v>
+        <v>283</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -3933,16 +3953,16 @@
         <v>4</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>315</v>
+        <v>284</v>
       </c>
       <c r="C5" s="13" t="s">
-        <v>316</v>
+        <v>285</v>
       </c>
       <c r="D5" s="13">
         <v>4</v>
       </c>
       <c r="E5" s="13" t="s">
-        <v>317</v>
+        <v>286</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -3950,16 +3970,16 @@
         <v>5</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>345</v>
+        <v>308</v>
       </c>
       <c r="C6" s="13" t="s">
-        <v>318</v>
+        <v>287</v>
       </c>
       <c r="D6" s="13">
         <v>5</v>
       </c>
       <c r="E6" s="13" t="s">
-        <v>319</v>
+        <v>288</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -3967,16 +3987,16 @@
         <v>6</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="C7" s="13" t="s">
-        <v>320</v>
+        <v>336</v>
       </c>
       <c r="D7" s="13">
         <v>6</v>
       </c>
       <c r="E7" s="13" t="s">
-        <v>321</v>
+        <v>289</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -3984,16 +4004,16 @@
         <v>7</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="C8" s="13" t="s">
-        <v>322</v>
+        <v>337</v>
       </c>
       <c r="D8" s="13">
         <v>7</v>
       </c>
       <c r="E8" s="13" t="s">
-        <v>323</v>
+        <v>290</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -4001,16 +4021,16 @@
         <v>8</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>324</v>
+        <v>291</v>
       </c>
       <c r="C9" s="13" t="s">
-        <v>325</v>
+        <v>338</v>
       </c>
       <c r="D9" s="13">
         <v>8</v>
       </c>
       <c r="E9" s="13" t="s">
-        <v>326</v>
+        <v>292</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -4018,16 +4038,16 @@
         <v>9</v>
       </c>
       <c r="B10" s="13" t="s">
-        <v>324</v>
+        <v>291</v>
       </c>
       <c r="C10" s="13" t="s">
-        <v>327</v>
+        <v>339</v>
       </c>
       <c r="D10" s="13">
         <v>9</v>
       </c>
       <c r="E10" s="13" t="s">
-        <v>326</v>
+        <v>292</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -4035,16 +4055,16 @@
         <v>10</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>324</v>
+        <v>291</v>
       </c>
       <c r="C11" s="13" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="D11" s="13">
         <v>10</v>
       </c>
       <c r="E11" s="13" t="s">
-        <v>329</v>
+        <v>293</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -4052,16 +4072,16 @@
         <v>11</v>
       </c>
       <c r="B12" s="13" t="s">
-        <v>324</v>
+        <v>291</v>
       </c>
       <c r="C12" s="13" t="s">
-        <v>330</v>
+        <v>341</v>
       </c>
       <c r="D12" s="13">
         <v>11</v>
       </c>
       <c r="E12" s="13" t="s">
-        <v>329</v>
+        <v>293</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -4069,16 +4089,16 @@
         <v>12</v>
       </c>
       <c r="B13" s="13" t="s">
-        <v>324</v>
+        <v>291</v>
       </c>
       <c r="C13" s="13" t="s">
-        <v>331</v>
+        <v>294</v>
       </c>
       <c r="D13" s="13">
         <v>12</v>
       </c>
       <c r="E13" s="13" t="s">
-        <v>319</v>
+        <v>288</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -4086,16 +4106,16 @@
         <v>13</v>
       </c>
       <c r="B14" s="13" t="s">
-        <v>324</v>
+        <v>291</v>
       </c>
       <c r="C14" s="13" t="s">
-        <v>332</v>
+        <v>295</v>
       </c>
       <c r="D14" s="13">
         <v>13</v>
       </c>
       <c r="E14" s="13" t="s">
-        <v>319</v>
+        <v>288</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -4103,16 +4123,16 @@
         <v>14</v>
       </c>
       <c r="B15" s="13" t="s">
-        <v>324</v>
+        <v>291</v>
       </c>
       <c r="C15" s="13" t="s">
-        <v>333</v>
+        <v>296</v>
       </c>
       <c r="D15" s="13">
         <v>14</v>
       </c>
       <c r="E15" s="13" t="s">
-        <v>334</v>
+        <v>297</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -4120,16 +4140,16 @@
         <v>15</v>
       </c>
       <c r="B16" s="13" t="s">
-        <v>324</v>
+        <v>291</v>
       </c>
       <c r="C16" s="13" t="s">
-        <v>335</v>
+        <v>298</v>
       </c>
       <c r="D16" s="13">
         <v>15</v>
       </c>
       <c r="E16" s="13" t="s">
-        <v>336</v>
+        <v>299</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -4137,16 +4157,16 @@
         <v>16</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>337</v>
+        <v>300</v>
       </c>
       <c r="C17" s="13" t="s">
-        <v>338</v>
+        <v>301</v>
       </c>
       <c r="D17" s="13">
         <v>16</v>
       </c>
       <c r="E17" s="13" t="s">
-        <v>339</v>
+        <v>302</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -4154,16 +4174,16 @@
         <v>17</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>340</v>
+        <v>303</v>
       </c>
       <c r="C18" s="13" t="s">
-        <v>341</v>
+        <v>304</v>
       </c>
       <c r="D18" s="13">
         <v>17</v>
       </c>
       <c r="E18" s="13" t="s">
-        <v>342</v>
+        <v>305</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -4171,21 +4191,21 @@
         <v>18</v>
       </c>
       <c r="B19" s="13" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C19" s="13" t="s">
-        <v>343</v>
+        <v>306</v>
       </c>
       <c r="D19" s="13">
         <v>18</v>
       </c>
       <c r="E19" s="13" t="s">
-        <v>344</v>
+        <v>307</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" t="s">
-        <v>303</v>
+        <v>342</v>
       </c>
     </row>
   </sheetData>
